--- a/exports/trend_1d/ETERNAL_full_report.xlsx
+++ b/exports/trend_1d/ETERNAL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>24.75</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44546</v>
+        <v>44547</v>
       </c>
       <c r="H2" t="n">
-        <v>138.4</v>
+        <v>135.35</v>
       </c>
       <c r="I2" t="n">
         <v>135.8386069838922</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K2" t="n">
-        <v>5.37</v>
+        <v>3.05</v>
       </c>
       <c r="L2" t="n">
         <v>8.26</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.99</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44708</v>
+        <v>44711</v>
       </c>
       <c r="H3" t="n">
-        <v>62.05</v>
+        <v>71.05</v>
       </c>
       <c r="I3" t="n">
         <v>65.4850971266754</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K3" t="n">
-        <v>54.16</v>
+        <v>47.51</v>
       </c>
       <c r="L3" t="n">
         <v>5.25</v>
@@ -612,7 +647,7 @@
         <v>4.51</v>
       </c>
       <c r="N3" t="n">
-        <v>13.85</v>
+        <v>14.5</v>
       </c>
       <c r="O3" t="n">
         <v>-2.2</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>26.29</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44740</v>
+        <v>44741</v>
       </c>
       <c r="H4" t="n">
-        <v>60.3</v>
+        <v>57.3</v>
       </c>
       <c r="I4" t="n">
         <v>59.52411723073502</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K4" t="n">
-        <v>-15.13</v>
+        <v>-19.35</v>
       </c>
       <c r="L4" t="n">
-        <v>16.05</v>
+        <v>19.99</v>
       </c>
       <c r="M4" t="n">
         <v>4.89</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>27.28</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44774</v>
+        <v>44775</v>
       </c>
       <c r="H5" t="n">
-        <v>46.3</v>
+        <v>55.55</v>
       </c>
       <c r="I5" t="n">
         <v>52.90251101911152</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K5" t="n">
-        <v>19.2</v>
+        <v>3.05</v>
       </c>
       <c r="L5" t="n">
         <v>7.33</v>
       </c>
       <c r="M5" t="n">
-        <v>2.16</v>
+        <v>7.99</v>
       </c>
       <c r="N5" t="n">
-        <v>5.52</v>
+        <v>19.98</v>
       </c>
       <c r="O5" t="n">
         <v>-4.98</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>27.23</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44887</v>
+        <v>44888</v>
       </c>
       <c r="H6" t="n">
-        <v>63.95</v>
+        <v>61.75</v>
       </c>
       <c r="I6" t="n">
         <v>62.37081564568232</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K6" t="n">
-        <v>15.12</v>
+        <v>11.16</v>
       </c>
       <c r="L6" t="n">
         <v>12.87</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>15.79</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45036</v>
+        <v>45037</v>
       </c>
       <c r="H7" t="n">
-        <v>54.2</v>
+        <v>56.05</v>
       </c>
       <c r="I7" t="n">
         <v>55.95749112383754</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K7" t="n">
-        <v>12.23</v>
+        <v>9.23</v>
       </c>
       <c r="L7" t="n">
         <v>11.74</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.54</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H8" t="n">
-        <v>156.9</v>
+        <v>148.65</v>
       </c>
       <c r="I8" t="n">
         <v>151.4332666059327</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K8" t="n">
-        <v>179.93</v>
+        <v>165.21</v>
       </c>
       <c r="L8" t="n">
         <v>3.48</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>224</v>
+        <v>225</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>18.36</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45373</v>
+        <v>45377</v>
       </c>
       <c r="H9" t="n">
-        <v>174.2</v>
+        <v>182.6</v>
       </c>
       <c r="I9" t="n">
         <v>175.4583675305089</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>-17.19</v>
+        <v>-22.84</v>
       </c>
       <c r="L9" t="n">
-        <v>17.66</v>
+        <v>23.55</v>
       </c>
       <c r="M9" t="n">
         <v>1.53</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>15.57</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c r="H10" t="n">
-        <v>179.15</v>
+        <v>175.45</v>
       </c>
       <c r="I10" t="n">
         <v>178.2355291829821</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.89</v>
+        <v>-3.92</v>
       </c>
       <c r="L10" t="n">
         <v>6.22</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>16.11</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45461</v>
+        <v>45462</v>
       </c>
       <c r="H11" t="n">
-        <v>188.61</v>
+        <v>198.49</v>
       </c>
       <c r="I11" t="n">
         <v>191.5770154146641</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.5</v>
+        <v>-13.13</v>
       </c>
       <c r="L11" t="n">
-        <v>7.78</v>
+        <v>14.56</v>
       </c>
       <c r="M11" t="n">
         <v>2.99</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>13.6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45582</v>
+        <v>45583</v>
       </c>
       <c r="H12" t="n">
-        <v>270.55</v>
+        <v>257.45</v>
       </c>
       <c r="I12" t="n">
         <v>263.4240099301971</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K12" t="n">
-        <v>36.3</v>
+        <v>29.7</v>
       </c>
       <c r="L12" t="n">
         <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.18</v>
+        <v>5.05</v>
       </c>
       <c r="N12" t="n">
         <v>5.09</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.45</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="H13" t="n">
-        <v>273.31</v>
+        <v>280.11</v>
       </c>
       <c r="I13" t="n">
         <v>273.9678867884302</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.16</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>10.44</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>12.54</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45660</v>
+        <v>45663</v>
       </c>
       <c r="H14" t="n">
-        <v>272.85</v>
+        <v>264.85</v>
       </c>
       <c r="I14" t="n">
         <v>270.0595908524035</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.59</v>
+        <v>-5.45</v>
       </c>
       <c r="L14" t="n">
-        <v>3.93</v>
+        <v>6.39</v>
       </c>
       <c r="M14" t="n">
         <v>2.91</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>12.85</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="H15" t="n">
-        <v>222.08</v>
+        <v>231.6</v>
       </c>
       <c r="I15" t="n">
         <v>230.10398798752</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K15" t="n">
-        <v>16.15</v>
+        <v>12.55</v>
       </c>
       <c r="L15" t="n">
         <v>3.76</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>13.28</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="H16" t="n">
-        <v>338.1</v>
+        <v>328.35</v>
       </c>
       <c r="I16" t="n">
         <v>328.7791759742486</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K16" t="n">
-        <v>45.98</v>
+        <v>41.77</v>
       </c>
       <c r="L16" t="n">
         <v>4.99</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.41</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="H17" t="n">
-        <v>294.55</v>
+        <v>299.25</v>
       </c>
       <c r="I17" t="n">
         <v>296.6109270966321</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K17" t="n">
-        <v>10.29</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L17" t="n">
         <v>4.46</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H18" t="n">
-        <v>281.35</v>
+        <v>269.6</v>
       </c>
       <c r="I18" t="n">
         <v>271.668206326559</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.98</v>
+        <v>-9.91</v>
       </c>
       <c r="L18" t="n">
-        <v>7.55</v>
+        <v>10.49</v>
       </c>
       <c r="M18" t="n">
         <v>1.74</v>
       </c>
       <c r="N18" t="n">
-        <v>3.86</v>
+        <v>4.18</v>
       </c>
       <c r="O18" t="n">
         <v>1.6</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>12.56</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H19" t="n">
-        <v>279.8</v>
+        <v>294.15</v>
       </c>
       <c r="I19" t="n">
         <v>294.1214092754464</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.78</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L19" t="n">
         <v>13.13</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>18.83</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="H20" t="n">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="I20" t="n">
         <v>264.0383426241287</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.890000000000001</v>
+        <v>-13.65</v>
       </c>
       <c r="L20" t="n">
-        <v>9.960000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5</v>
+        <v>2.99</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>5.22</v>
       </c>
       <c r="O20" t="n">
         <v>5.13</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>14.95</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H21" t="n">
-        <v>246.67</v>
+        <v>252.7</v>
       </c>
       <c r="I21" t="n">
         <v>247.8686554269398</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K21" t="n">
-        <v>2.89</v>
+        <v>0.51</v>
       </c>
       <c r="L21" t="n">
         <v>4.29</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>12.13</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H22" t="n">
-        <v>320</v>
+        <v>313.9</v>
       </c>
       <c r="I22" t="n">
         <v>319.8099386352187</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K22" t="n">
-        <v>26.63</v>
+        <v>24.22</v>
       </c>
       <c r="L22" t="n">
         <v>7.55</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1755,6 +2030,14 @@
       <c r="Q23" t="n">
         <v>18</v>
       </c>
+      <c r="R23" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4061,7 +4344,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>88.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -4071,7 +4354,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -4081,7 +4364,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8">
@@ -4091,7 +4374,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -4101,7 +4384,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -4111,7 +4394,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -4151,7 +4434,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.91</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="15">
@@ -4161,7 +4444,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24.99</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="16">
@@ -4171,7 +4454,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8.029999999999999</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="17">
@@ -4181,7 +4464,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>179.93</v>
+        <v>165.21</v>
       </c>
     </row>
     <row r="18">
@@ -4201,7 +4484,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.15</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="20">
@@ -4221,7 +4504,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.66</v>
+        <v>23.55</v>
       </c>
     </row>
     <row r="22">
@@ -4231,7 +4514,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -4241,7 +4524,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -4251,7 +4534,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.42</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="25">
@@ -4261,7 +4544,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.83</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="26">
@@ -4271,7 +4554,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.14</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="27">
@@ -4281,7 +4564,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.85</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="28">
@@ -4291,7 +4574,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
